--- a/deliverables/04_project_plan/project_plan.xlsx
+++ b/deliverables/04_project_plan/project_plan.xlsx
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L56"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -629,13 +629,15 @@
     <col width="25" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>PROJECT PLAN — Waterfall backbone (sprint details in SPRINT BACKLOG sheet)</t>
-        </is>
-      </c>
-    </row>
+          <t>ПРОЕКТЕН ПЛАН — Waterfall основа (sprint детайли в SPRINT BACKLOG sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -755,7 +757,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Иницииране</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
@@ -804,7 +806,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Project charter &amp; scope</t>
+          <t>Project charter &amp; обхват</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -857,12 +859,12 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Team formation &amp; onboarding</t>
+          <t>Формиране на екип &amp; onboarding</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Team assembled</t>
+          <t>Екип сформиран</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -910,12 +912,12 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Kickoff + baseline plan</t>
+          <t>Kickoff + baseline план</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Baseline Gantt + initial backlog</t>
+          <t>Baseline Gantt + първоначален backlog</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -963,7 +965,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Requirements Analysis</t>
+          <t>Анализ на изискванията</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr"/>
@@ -1012,12 +1014,12 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Business requirements workshops</t>
+          <t>Workshops за бизнес изисквания</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Business Req Doc</t>
+          <t>Business Req документ</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1065,12 +1067,12 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Regulatory requirements</t>
+          <t>Регулаторни изисквания</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Regulatory Req Doc</t>
+          <t>Regulatory Req документ</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1118,12 +1120,12 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Non-functional requirements</t>
+          <t>Нефункционални изисквания</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>NFR Doc</t>
+          <t>NFR документ</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1171,12 +1173,12 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>User personas &amp; journey mapping</t>
+          <t>Персони и journey mapping</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Personas + journeys</t>
+          <t>Персони + journeys</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1224,7 +1226,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Initial Product Backlog (for P3 sprints)</t>
+          <t>Първоначален Product Backlog (за P3 sprints)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1277,12 +1279,12 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Requirements review &amp; sign-off</t>
+          <t>Преглед и sign-off на изискванията</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>✋ GATE 1: Requirements sign-off</t>
+          <t>GATE 1: Sign-off на изискванията</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -1330,7 +1332,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Дизайн</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -1379,12 +1381,12 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Solution architecture</t>
+          <t>Solution архитектура</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Architecture Doc + .drawio</t>
+          <t>Architecture документ + .drawio</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -1432,7 +1434,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Data model &amp; DB schemas</t>
+          <t>Data model и DB схеми</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -1485,12 +1487,12 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>UI/UX design</t>
+          <t>UI/UX дизайн</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Figma mockups + prototype</t>
+          <t>Figma mockups + прототип</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -1538,12 +1540,12 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>API contracts &amp; integration design</t>
+          <t>API contracts и дизайн на интеграцията</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>OpenAPI specs + integration diagram</t>
+          <t>OpenAPI specs + integration диаграма</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -1591,12 +1593,12 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Security design &amp; threat model</t>
+          <t>Security дизайн и threat model</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Threat model + security architecture</t>
+          <t>Threat model + security архитектура</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -1644,12 +1646,12 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Sprint-level estimation &amp; backlog refinement</t>
+          <t>Sprint-level estimation и backlog refinement</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Estimated backlog mapped to 8 sprints</t>
+          <t>Estimated backlog разпределен в 8 спринта</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -1697,12 +1699,12 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Design review &amp; sign-off</t>
+          <t>Преглед и sign-off на дизайна</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>✋ GATE 2: Design sign-off</t>
+          <t>GATE 2: Sign-off на дизайна</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -1782,7 +1784,7 @@
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>🌀 AGILE</t>
+          <t>AGILE</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1801,7 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Sprint 1: Infrastructure Foundation</t>
+          <t>Sprint 1: Инфраструктурна основа</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
@@ -1835,7 +1837,7 @@
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>🌀 Sprint</t>
+          <t>Sprint</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1854,12 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Sprint 2: CMS Core Registration</t>
+          <t>Sprint 2: CMS Core регистрация</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Ref# generation, complaint CRUD, Camunda workflow</t>
+          <t>Ref# генериране, CRUD за жалба, Camunda workflow</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -1888,7 +1890,7 @@
       </c>
       <c r="L27" s="15" t="inlineStr">
         <is>
-          <t>🌀 Sprint</t>
+          <t>Sprint</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1907,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Sprint 3: Audit + Compliance Core</t>
+          <t>Sprint 3: Одит + Compliance Core</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
@@ -1941,7 +1943,7 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>🌀 Sprint</t>
+          <t>Sprint</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1960,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Sprint 4: Notifications Multi-channel</t>
+          <t>Sprint 4: Многоканални нотификации</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -1994,7 +1996,7 @@
       </c>
       <c r="L29" s="15" t="inlineStr">
         <is>
-          <t>🌀 Sprint</t>
+          <t>Sprint</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2018,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Queue, detail view, decision recording, approval flow</t>
+          <t>Опашка, детайлен изглед, записване на решения, approval flow</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -2047,7 +2049,7 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>🌀 Sprint</t>
+          <t>Sprint</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2066,12 @@
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>Sprint 6: Client-facing (BBM + BBO)</t>
+          <t>Sprint 6: Клиентска част (BBM + BBO)</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>In-app complaint form, attachments, status tracking</t>
+          <t>In-app формуляр за жалба, прикачени файлове, status tracking</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -2100,7 +2102,7 @@
       </c>
       <c r="L31" s="15" t="inlineStr">
         <is>
-          <t>🌀 Sprint</t>
+          <t>Sprint</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2119,12 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Sprint 7: Core Banking + Card System Integration</t>
+          <t>Sprint 7: Core Banking + Card System интеграция</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Integration adapters, compensation via CORE_ACC</t>
+          <t>Integration адаптери, компенсация през CORE_ACC</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -2153,7 +2155,7 @@
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>🌀 Sprint (holiday skip)</t>
+          <t>Sprint (holiday skip)</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2172,7 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>Sprint 8: Reporting + Escalation + Polish</t>
+          <t>Sprint 8: Отчети + ескалация + полиране</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -2206,7 +2208,7 @@
       </c>
       <c r="L33" s="15" t="inlineStr">
         <is>
-          <t>🌀 Sprint</t>
+          <t>Sprint</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2225,7 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>Testing (AGILE test cycles)</t>
+          <t>Тестване (Agile test cycles)</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr"/>
@@ -2255,7 +2257,7 @@
       </c>
       <c r="L34" s="17" t="inlineStr">
         <is>
-          <t>🌀 AGILE</t>
+          <t>AGILE</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2279,7 @@
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>SIT report cycle 1</t>
+          <t>SIT отчет цикъл 1</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2308,7 +2310,7 @@
       </c>
       <c r="L35" s="15" t="inlineStr">
         <is>
-          <t>🌀 Test sprint</t>
+          <t>Test sprint</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2332,7 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>Compliance + Security test reports</t>
+          <t>Compliance + Security test отчети</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
@@ -2361,7 +2363,7 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>🌀 Test sprint</t>
+          <t>Test sprint</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2385,7 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>Perf test report + UAT sign-off</t>
+          <t>Perf test отчет + UAT sign-off</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
@@ -2414,7 +2416,7 @@
       </c>
       <c r="L37" s="15" t="inlineStr">
         <is>
-          <t>🌀 Test sprint</t>
+          <t>Test sprint</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2433,12 @@
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>Test Cycle 4: Regulator review + fixes</t>
+          <t>Test Cycle 4: Преглед от регулатор + fixes</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>Regulator approval + residual fixes</t>
+          <t>Одобрение от регулатор + residual fixes</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -2467,7 +2469,7 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>🌀 Test sprint</t>
+          <t>Test sprint</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2486,12 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Go/no-go decision</t>
+          <t>Go/no-go решение</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>✋ GATE 3: Go/no-go</t>
+          <t>GATE 3: Go/no-go</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
@@ -2591,7 +2593,7 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>System in production</t>
+          <t>Системата в production</t>
         </is>
       </c>
       <c r="F41" s="18" t="inlineStr">
@@ -2639,12 +2641,12 @@
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>Pilot launch (5%)</t>
+          <t>Пилотно пускане (5%)</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>Pilot live</t>
+          <t>Пилот стартирал</t>
         </is>
       </c>
       <c r="F42" s="18" t="inlineStr">
@@ -2750,7 +2752,7 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>🎉 GO LIVE — 100%</t>
+          <t>GO LIVE — 100%</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
@@ -2798,7 +2800,7 @@
       </c>
       <c r="D45" s="21" t="inlineStr">
         <is>
-          <t>Hypercare / Stabilization (Kanban)</t>
+          <t>Hypercare / Стабилизация (Kanban)</t>
         </is>
       </c>
       <c r="E45" s="21" t="inlineStr"/>
@@ -2830,7 +2832,7 @@
       </c>
       <c r="L45" s="21" t="inlineStr">
         <is>
-          <t>🌀 Kanban</t>
+          <t>Kanban</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2849,7 @@
       </c>
       <c r="D46" s="21" t="inlineStr">
         <is>
-          <t>Hypercare 24/7 support</t>
+          <t>Hypercare 24/7 поддръжка</t>
         </is>
       </c>
       <c r="E46" s="21" t="inlineStr">
@@ -2905,7 +2907,7 @@
       </c>
       <c r="E47" s="21" t="inlineStr">
         <is>
-          <t>Tuning report</t>
+          <t>Tuning отчет</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
@@ -2953,12 +2955,12 @@
       </c>
       <c r="D48" s="21" t="inlineStr">
         <is>
-          <t>Retrospective + Release 2 prep</t>
+          <t>Retrospective + подготовка за Release 2</t>
         </is>
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>Retro doc + Release 2 backlog draft</t>
+          <t>Retro документ + Release 2 backlog draft</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
@@ -3006,12 +3008,12 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Release 1 closure</t>
+          <t>Release 1 закриване</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>✋ GATE 4: Release 1 accepted</t>
+          <t>GATE 4: Release 1 приет</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
@@ -3108,12 +3110,12 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>AI scope requirements + backlog</t>
+          <t>AI scope изисквания + backlog</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>AI Req Doc + initial backlog</t>
+          <t>AI Req документ + първоначален backlog</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -3161,7 +3163,7 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>AI architecture + design (1 gate)</t>
+          <t>AI архитектура + дизайн (1 gate)</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -3219,7 +3221,7 @@
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>AI modules v1</t>
+          <t>AI модули v1</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -3250,7 +3252,7 @@
       </c>
       <c r="L53" s="14" t="inlineStr">
         <is>
-          <t>🌀 Pure Scrum</t>
+          <t>Pure Scrum</t>
         </is>
       </c>
     </row>
@@ -3267,12 +3269,12 @@
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>AI testing &amp; compliance re-check</t>
+          <t>AI тестване &amp; compliance преглед</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>AI test report</t>
+          <t>AI test отчет</t>
         </is>
       </c>
       <c r="F54" s="16" t="inlineStr">
@@ -3320,7 +3322,7 @@
       </c>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>AI deployment (gradual rollout)</t>
+          <t>AI deployment (постепенен rollout)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
@@ -3378,7 +3380,7 @@
       </c>
       <c r="E56" s="21" t="inlineStr">
         <is>
-          <t>Release 2 closed</t>
+          <t>Release 2 закрит</t>
         </is>
       </c>
       <c r="F56" s="20" t="inlineStr">
@@ -3439,14 +3441,14 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>PROJECT DETAILS</t>
+          <t>ДЕТАЙЛИ ЗА ПРОЕКТА</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>PROJECT NUMBER</t>
+          <t>НОМЕР НА ПРОЕКТА</t>
         </is>
       </c>
       <c r="C4" s="23" t="inlineStr">
@@ -3458,7 +3460,7 @@
     <row r="5">
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>PROJECT NAME</t>
+          <t>НАИМЕНОВАНИЕ</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -3470,7 +3472,7 @@
     <row r="6">
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>METHODOLOGY</t>
+          <t>МЕТОДОЛОГИЯ</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -3482,7 +3484,7 @@
     <row r="7">
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>GOVERNANCE LAYER</t>
+          <t>УПРАВЛЕНСКИ СЛОЙ</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -3494,7 +3496,7 @@
     <row r="8">
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>DELIVERY LAYER (inside P3 + P4)</t>
+          <t>ИЗПЪЛНИТЕЛСКИ СЛОЙ (в P3 + P4)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -3530,7 +3532,7 @@
     <row r="11">
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>RELEASE 1 IMPLEMENTATION SPRINTS</t>
+          <t>RELEASE 1 СПРИНТОВЕ</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -3542,7 +3544,7 @@
     <row r="12">
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>RELEASE 1 TEST CYCLES</t>
+          <t>RELEASE 1 ТЕСТОВИ ЦИКЛИ</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -3554,7 +3556,7 @@
     <row r="13">
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>TOTAL PROGRAM DURATION</t>
+          <t>ОБЩА ПРОДЪЛЖИТЕЛНОСТ</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -3566,7 +3568,7 @@
     <row r="14">
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>TEAM SIZE</t>
+          <t>РАЗМЕР НА ЕКИПА</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -3578,7 +3580,7 @@
     <row r="15">
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>PROJECT SPONSOR</t>
+          <t>СПОНСОР НА ПРОЕКТА</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -3602,7 +3604,7 @@
     <row r="17">
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>PROJECT MANAGER</t>
+          <t>ПРОЕКТЕН МЕНИДЖЪР</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -3638,7 +3640,7 @@
     <row r="20">
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>TEAM MEMBERS</t>
+          <t>ЧЛЕНОВЕ НА ЕКИПА</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -3650,7 +3652,7 @@
     <row r="21">
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>ДАТА</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -3662,7 +3664,7 @@
     <row r="22">
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>VERSION</t>
+          <t>ВЕРСИЯ</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -3674,7 +3676,7 @@
     <row r="23">
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>VARIANT</t>
+          <t>ВАРИАНТ</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -3697,7 +3699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J57"/>
+  <dimension ref="A2:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -3746,22 +3748,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Estimate (SP)</t>
+          <t>Оценка (SP)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Приоритет</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Task Owner</t>
+          <t>Отговорник</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Effort (h)</t>
+          <t>Усилие (ч)</t>
         </is>
       </c>
     </row>
@@ -5328,10 +5330,11 @@
     <row r="46">
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>SPRINT SUMMARY</t>
-        </is>
-      </c>
-    </row>
+          <t>ОБОБЩЕНИЕ НА СПРИНТОВЕТЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="B48" s="2" t="inlineStr">
         <is>
@@ -5350,12 +5353,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>Часове</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Focus</t>
+          <t>Фокус</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5379,7 @@
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>Infrastructure Foundation</t>
+          <t>Инфраструктурна основа</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5400,7 @@
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>CMS Core Registration</t>
+          <t>CMS Core регистрация</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5421,7 @@
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>Audit + Compliance Core</t>
+          <t>Одит + Compliance Core</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5442,7 @@
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>Notifications Multi-channel</t>
+          <t>Многоканални нотификации</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5484,7 @@
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>Client-facing (BBM + BBO)</t>
+          <t>Клиентска част (BBM + BBO)</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5505,7 @@
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>Core Banking + Card Integration</t>
+          <t>Core Banking + Card интеграция</t>
         </is>
       </c>
     </row>
@@ -5523,14 +5526,14 @@
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>Reporting, Escalation &amp; Polish</t>
+          <t>Отчети, ескалация &amp; полиране</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="30" t="inlineStr">
         <is>
-          <t>TOTAL Release 1 impl</t>
+          <t>Общо Release 1 имплементация</t>
         </is>
       </c>
       <c r="C57" s="30" t="n">
@@ -5544,7 +5547,7 @@
       </c>
       <c r="F57" s="31" t="inlineStr">
         <is>
-          <t>~22 week equivalent</t>
+          <t>~22 седмици еквивалент</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H11"/>
+  <dimension ref="A2:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -5577,7 +5580,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Waterfall Phases, Delivery Mode &amp; Sign-off Gates</t>
+          <t>Waterfall фази, delivery mode &amp; sign-off gates</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5629,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Иницииране</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -5641,7 +5644,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Charter, Team</t>
+          <t>Charter, екип</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -5663,7 +5666,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Requirements Analysis</t>
+          <t>Анализ на изискванията</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -5678,7 +5681,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Business + Regulatory + NFR + Personas + initial Backlog</t>
+          <t>Business + Regulatory + NFR + Персони + първоначален Backlog</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -5688,7 +5691,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>✋ GATE 1</t>
+          <t>GATE 1</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5703,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Дизайн</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -5715,7 +5718,7 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Architecture, Data model, UI/UX, APIs, Security, sprint-level estimation</t>
+          <t>Архитектура, Data model, UI/UX, APIs, Security, sprint-level estimation</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -5725,7 +5728,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>✋ GATE 2</t>
+          <t>GATE 2</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5740,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Имплементация</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -5747,12 +5750,12 @@
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>🌀 AGILE (Scrum)</t>
+          <t>AGILE (Scrum)</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>User stories delivered sprint-by-sprint; sprint demos to PO/stakeholders</t>
+          <t>User stories доставени sprint-by-sprint; sprint демо към PO/стейкхолдери</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -5774,7 +5777,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Тестване</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -5784,12 +5787,12 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>🌀 AGILE (test sprints)</t>
+          <t>AGILE (test sprints)</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>SIT, Compliance, Security, Performance, UAT, Regulator review</t>
+          <t>SIT, Compliance, Security, Performance, UAT, преглед от регулатор</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -5799,7 +5802,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>✋ GATE 3 — Go/no-go</t>
+          <t>GATE 3 — Go/no-go</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5829,7 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>Production deploy, Pilot (5%), GA</t>
+          <t>Production deploy, пилот (5%), GA</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -5836,7 +5839,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>🎉 GO LIVE</t>
+          <t>GO LIVE</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5861,12 @@
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>🌀 Kanban</t>
+          <t>Kanban</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t>Incident resolution, Tuning, Retrospective</t>
+          <t>Incident resolution, tuning, retrospective</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -5873,7 +5876,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>✋ GATE 4</t>
+          <t>GATE 4</t>
         </is>
       </c>
     </row>
@@ -5899,21 +5902,21 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>RESOURCES</t>
+          <t>РЕСУРСИ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="28" t="inlineStr">
         <is>
-          <t>Team Composition — Release 1 (Level 1)</t>
+          <t>Състав на екипа — Release 1 (Level 1)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Роля</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5923,7 +5926,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Responsibility</t>
+          <t>Отговорност</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6193,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Risk Register</t>
+          <t>Регистър на рисковете</t>
         </is>
       </c>
     </row>
@@ -6202,37 +6205,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Phase</t>
+          <t>Фаза</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Риск</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Likelihood</t>
+          <t>Вероятност</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Ефект</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Оценка</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Mitigation</t>
+          <t>Мярка</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Отговорник</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M20"/>
+  <dimension ref="A2:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -6749,7 +6752,7 @@
     <row r="4">
       <c r="B4" s="28" t="inlineStr">
         <is>
-          <t>PHASE</t>
+          <t>ФАЗА</t>
         </is>
       </c>
       <c r="E4" s="28" t="inlineStr">
@@ -6764,17 +6767,17 @@
       </c>
       <c r="I4" s="28" t="inlineStr">
         <is>
-          <t>PRIORITY</t>
+          <t>ПРИОРИТЕТ</t>
         </is>
       </c>
       <c r="K4" s="28" t="inlineStr">
         <is>
-          <t>LIKELIHOOD / IMPACT</t>
+          <t>ВЕРОЯТНОСТ / ЕФЕКТ</t>
         </is>
       </c>
       <c r="M4" s="28" t="inlineStr">
         <is>
-          <t>OWNER</t>
+          <t>ОТГОВОРНИК</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6789,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P0 Initiation</t>
+          <t>P0 Иницииране</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -6817,7 +6820,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P1 Requirements</t>
+          <t>P1 Изисквания</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -6848,7 +6851,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P2 Design</t>
+          <t>P2 Дизайн</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -6879,7 +6882,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P3 Implementation</t>
+          <t>P3 Имплементация</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -6905,7 +6908,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P4 Testing</t>
+          <t>P4 Тестване</t>
         </is>
       </c>
       <c r="E9" t="n">
